--- a/data/trans_orig/P36BPD14_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023</t>
+          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>46366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>42156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73424</t>
+          <t>73071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145367</t>
+          <t>149004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214570</t>
+          <t>214214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111779</t>
+          <t>114260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159305</t>
+          <t>158436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279495</t>
+          <t>275738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359727</t>
+          <t>358483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162757</t>
+          <t>160286</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232673</t>
+          <t>230972</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122663</t>
+          <t>122186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169825</t>
+          <t>169508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>299739</t>
+          <t>300386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>382636</t>
+          <t>382074</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71443</t>
+          <t>71235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>48122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58041</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109062</t>
+          <t>110740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147531</t>
+          <t>146943</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>196922</t>
+          <t>198842</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117664</t>
+          <t>116179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>227740</t>
+          <t>228159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>274718</t>
+          <t>265717</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405582</t>
+          <t>407675</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179527</t>
+          <t>175121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231533</t>
+          <t>231302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244148</t>
+          <t>244078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>382286</t>
+          <t>373556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>442224</t>
+          <t>439881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>597961</t>
+          <t>603063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>55100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>80556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93642</t>
+          <t>95954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132169</t>
+          <t>133675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206409</t>
+          <t>207605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254885</t>
+          <t>255161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200153</t>
+          <t>200113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240037</t>
+          <t>240605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418833</t>
+          <t>418851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483139</t>
+          <t>480759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238957</t>
+          <t>237909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286617</t>
+          <t>284826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234017</t>
+          <t>233578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273656</t>
+          <t>273831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484474</t>
+          <t>485127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548826</t>
+          <t>546186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>29045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100543</t>
+          <t>102478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75532</t>
+          <t>73978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158765</t>
+          <t>158727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104115</t>
+          <t>110835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339163</t>
+          <t>336815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>270123</t>
+          <t>269442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366114</t>
+          <t>363118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298977</t>
+          <t>317568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>649804</t>
+          <t>651066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>459667</t>
+          <t>456620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>756191</t>
+          <t>739414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>292534</t>
+          <t>298614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379755</t>
+          <t>380680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>805656</t>
+          <t>801376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1229300</t>
+          <t>1207960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62715</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83344</t>
+          <t>82976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115739</t>
+          <t>115834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237625</t>
+          <t>235748</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282391</t>
+          <t>280878</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212315</t>
+          <t>211724</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>244499</t>
+          <t>244895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>461813</t>
+          <t>462366</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>518704</t>
+          <t>515778</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230890</t>
+          <t>232540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>274207</t>
+          <t>275163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250049</t>
+          <t>250101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283376</t>
+          <t>283900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>488768</t>
+          <t>492018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>548240</t>
+          <t>548832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37470</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71949</t>
+          <t>73503</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98513</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145289</t>
+          <t>147944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177075</t>
+          <t>177591</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275048</t>
+          <t>275778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>179821</t>
+          <t>185193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>438920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>158133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188461</t>
+          <t>187058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264682</t>
+          <t>263234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>517807</t>
+          <t>516976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>436745</t>
+          <t>438747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>750732</t>
+          <t>746870</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27206</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43596</t>
+          <t>44072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63681</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75749</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102312</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>123648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>150285</t>
+          <t>150628</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>191418</t>
+          <t>189906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>220355</t>
+          <t>218896</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>320685</t>
+          <t>320629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>361003</t>
+          <t>360912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96228</t>
+          <t>95314</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120410</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152426</t>
+          <t>151718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180029</t>
+          <t>180499</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>255743</t>
+          <t>254517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>295127</t>
+          <t>294410</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>229983</t>
+          <t>225319</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>336286</t>
+          <t>336566</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,82 +3937,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>334765</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>278361</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>375598</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>624924</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>547038</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>692037</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>334765</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>273694</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>372622</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>624924</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>534808</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>686337</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1093686</t>
+          <t>1105412</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1500316</t>
+          <t>1514335</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1182551</t>
+          <t>1186477</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1570080</t>
+          <t>1581264</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2433520</t>
+          <t>2463622</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3033221</t>
+          <t>3038526</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1636312</t>
+          <t>1625113</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2111407</t>
+          <t>2120096</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1722984</t>
+          <t>1715160</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2193738</t>
+          <t>2185959</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3403865</t>
+          <t>3400038</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4114980</t>
+          <t>4064753</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD14_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>49194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42156</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47936</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73071</t>
+          <t>81983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>180154</t>
+          <t>186277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149004</t>
+          <t>155590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214214</t>
+          <t>219840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134774</t>
+          <t>153024</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114260</t>
+          <t>129899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158436</t>
+          <t>178886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>314928</t>
+          <t>339301</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275738</t>
+          <t>298206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358483</t>
+          <t>377288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196325</t>
+          <t>194329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160286</t>
+          <t>159437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230972</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>174551</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122186</t>
+          <t>148272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169508</t>
+          <t>198597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>342229</t>
+          <t>368880</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>300386</t>
+          <t>329735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>382074</t>
+          <t>412671</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>305106</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305106</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305106</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>761771</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>761771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>705093</t>
+          <t>761771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49215</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71235</t>
+          <t>75772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48122</t>
+          <t>55321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82616</t>
+          <t>91758</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59134</t>
+          <t>71453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110740</t>
+          <t>119374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>171152</t>
+          <t>198188</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146943</t>
+          <t>169475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198842</t>
+          <t>227408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190016</t>
+          <t>220283</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116179</t>
+          <t>197111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>228159</t>
+          <t>243598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>361167</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>265717</t>
+          <t>382687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>407675</t>
+          <t>455443</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>203180</t>
+          <t>226586</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175121</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231302</t>
+          <t>254295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>288087</t>
+          <t>241158</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244078</t>
+          <t>214932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>373556</t>
+          <t>263863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>491267</t>
+          <t>467744</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>439881</t>
+          <t>430487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603063</t>
+          <t>501102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>55603</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60642</t>
+          <t>72937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67806</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>63375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80556</t>
+          <t>92906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111883</t>
+          <t>132032</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95954</t>
+          <t>111590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133675</t>
+          <t>154876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>229628</t>
+          <t>265744</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>239687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255161</t>
+          <t>291789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>219827</t>
+          <t>253102</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200113</t>
+          <t>230730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240605</t>
+          <t>274775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>449455</t>
+          <t>518845</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418851</t>
+          <t>487460</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480759</t>
+          <t>554718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262633</t>
+          <t>299490</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237909</t>
+          <t>273736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>284826</t>
+          <t>325459</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>254016</t>
+          <t>290910</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233578</t>
+          <t>269058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273831</t>
+          <t>314098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>516648</t>
+          <t>590400</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>485127</t>
+          <t>556864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>546186</t>
+          <t>626383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>541648</t>
+          <t>620440</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>541648</t>
+          <t>620440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>541648</t>
+          <t>620440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1077986</t>
+          <t>1241277</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1077986</t>
+          <t>1241277</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1077986</t>
+          <t>1241277</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62776</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>52004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102478</t>
+          <t>87064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59184</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46776</t>
+          <t>56897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>81658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121959</t>
+          <t>134986</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73978</t>
+          <t>116387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158727</t>
+          <t>155644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>236887</t>
+          <t>260279</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110835</t>
+          <t>235193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336815</t>
+          <t>289385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>298327</t>
+          <t>284929</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>269442</t>
+          <t>264833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363118</t>
+          <t>306494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>535214</t>
+          <t>545208</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>317568</t>
+          <t>514537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>651066</t>
+          <t>577360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>585322</t>
+          <t>370650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>456620</t>
+          <t>339934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>739414</t>
+          <t>397451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>354171</t>
+          <t>382461</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298614</t>
+          <t>362796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>380680</t>
+          <t>404718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>939493</t>
+          <t>753112</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>801376</t>
+          <t>722776</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1207960</t>
+          <t>789379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>697700</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>697700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>697700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711681</t>
+          <t>735606</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711681</t>
+          <t>735606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711681</t>
+          <t>735606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1596666</t>
+          <t>1433306</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1596666</t>
+          <t>1433306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1596666</t>
+          <t>1433306</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>42144</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51754</t>
+          <t>61286</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>74273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>98142</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82976</t>
+          <t>99607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115834</t>
+          <t>136134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>259835</t>
+          <t>279477</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235748</t>
+          <t>258005</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>280878</t>
+          <t>303487</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>228872</t>
+          <t>255885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211724</t>
+          <t>234825</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>244895</t>
+          <t>274650</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>488706</t>
+          <t>535362</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>462366</t>
+          <t>507585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>515778</t>
+          <t>566979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>252981</t>
+          <t>270884</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232540</t>
+          <t>246767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275163</t>
+          <t>293926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>266199</t>
+          <t>290575</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250101</t>
+          <t>271458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283900</t>
+          <t>310380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519180</t>
+          <t>561459</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492018</t>
+          <t>530482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>548832</t>
+          <t>591955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>559203</t>
+          <t>605782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559203</t>
+          <t>605782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559203</t>
+          <t>605782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546825</t>
+          <t>607746</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546825</t>
+          <t>607746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546825</t>
+          <t>607746</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106028</t>
+          <t>1213528</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106028</t>
+          <t>1213528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106028</t>
+          <t>1213528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>34512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>44662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45190</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73503</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>84152</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>71433</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98966</t>
+          <t>98838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>161542</t>
+          <t>177541</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147944</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177591</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>178381</t>
+          <t>195968</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>181519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275778</t>
+          <t>211161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>339923</t>
+          <t>373509</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185193</t>
+          <t>348602</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>438920</t>
+          <t>394539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>172772</t>
+          <t>189725</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158133</t>
+          <t>172855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187058</t>
+          <t>206271</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>384428</t>
+          <t>193202</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263234</t>
+          <t>176368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>516976</t>
+          <t>208078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>557200</t>
+          <t>382928</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>438747</t>
+          <t>360644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>746870</t>
+          <t>406927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>363056</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>363056</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>363056</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607999</t>
+          <t>438811</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607999</t>
+          <t>438811</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607999</t>
+          <t>438811</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>971055</t>
+          <t>840589</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>971055</t>
+          <t>840589</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>971055</t>
+          <t>840589</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>39605</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>53003</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>48773</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>98332</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>84934</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>113799</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>136875</t>
+          <t>150497</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>123648</t>
+          <t>135108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>150628</t>
+          <t>164158</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>204637</t>
+          <t>225051</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>189906</t>
+          <t>209523</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>218896</t>
+          <t>240387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>341512</t>
+          <t>375549</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>320629</t>
+          <t>354003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>360912</t>
+          <t>396956</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>117663</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95314</t>
+          <t>103226</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121169</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>166473</t>
+          <t>179032</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>164521</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180499</t>
+          <t>197057</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>274492</t>
+          <t>296695</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>254517</t>
+          <t>276007</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>294410</t>
+          <t>315485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>280347</t>
+          <t>307765</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>280347</t>
+          <t>307765</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>280347</t>
+          <t>307765</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424113</t>
+          <t>462810</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424113</t>
+          <t>462810</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424113</t>
+          <t>462810</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>704459</t>
+          <t>770575</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>704459</t>
+          <t>770575</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>704459</t>
+          <t>770575</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>290159</t>
+          <t>331214</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>225319</t>
+          <t>293997</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>336566</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>334765</t>
+          <t>380343</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278361</t>
+          <t>348575</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>375598</t>
+          <t>416155</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>624924</t>
+          <t>711557</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>547038</t>
+          <t>659977</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>692037</t>
+          <t>767367</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1376073</t>
+          <t>1518003</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1105412</t>
+          <t>1457276</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1514335</t>
+          <t>1581529</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1454832</t>
+          <t>1588242</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1186477</t>
+          <t>1536739</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1581264</t>
+          <t>1642008</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2830905</t>
+          <t>3106244</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2463622</t>
+          <t>3025277</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3038526</t>
+          <t>3194034</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1781231</t>
+          <t>1669328</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1625113</t>
+          <t>1600993</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2120096</t>
+          <t>1730392</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1859278</t>
+          <t>1751889</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1715160</t>
+          <t>1699075</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2185959</t>
+          <t>1808235</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3640508</t>
+          <t>3421217</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3400038</t>
+          <t>3334668</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4064753</t>
+          <t>3499752</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
